--- a/data/fmsForecastOutput/File1/RPT_RPT6724285789423RU_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6724285789423RU_fmsForecastOutput.xlsx
@@ -1884,7 +1884,7 @@
         <v>519.3851246249803</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>546.2416115148654</v>
+        <v>546.2416115148656</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>575.786858429019</v>
@@ -1899,7 +1899,7 @@
         <v>517.1632020171895</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>545.0023063966572</v>
+        <v>545.0023063966573</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>575.6489183257016</v>
@@ -1914,7 +1914,7 @@
         <v>68445515.84177998</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>77606177.464206</v>
+        <v>77606177.46420601</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>89958688.09397282</v>
@@ -1934,7 +1934,7 @@
         <v>637.3412090691777</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>670.2969966229873</v>
+        <v>670.2969966229874</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>706.5521808740002</v>
@@ -1949,7 +1949,7 @@
         <v>634.645385352844</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>668.7934014126074</v>
+        <v>668.7934014126075</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>706.3848279642939</v>
@@ -1964,7 +1964,7 @@
         <v>68445515.84177998</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>77606177.464206</v>
+        <v>77606177.46420601</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>89958688.09397282</v>
@@ -2377,7 +2377,7 @@
         <v>1571.25276800801</v>
       </c>
       <c r="W11" s="156" t="n">
-        <v>1615.640677369604</v>
+        <v>1615.640677369603</v>
       </c>
       <c r="X11" s="157" t="n">
         <v>1656.032835464363</v>
@@ -2392,7 +2392,7 @@
         <v>1569.852167210781</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>1615.640677369604</v>
+        <v>1615.640677369603</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>1656.032835464363</v>
@@ -2461,34 +2461,34 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>597.4513786571438</v>
+        <v>597.4513786571437</v>
       </c>
       <c r="D12" s="162" t="n">
         <v>628.120153338346</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>665.7798249418119</v>
+        <v>665.7798249418117</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>696.9518328815597</v>
+        <v>696.9518328815598</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>730.9963315245086</v>
+        <v>730.9963315245085</v>
       </c>
       <c r="H12" s="161" t="n">
-        <v>592.4869823605173</v>
+        <v>592.4869823605172</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>624.2162764899499</v>
+        <v>624.2162764899498</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>662.9661099624163</v>
+        <v>662.9661099624162</v>
       </c>
       <c r="K12" s="162" t="n">
         <v>695.3652629751867</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>730.7340279524723</v>
+        <v>730.734027952472</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>89436589.41894382</v>
@@ -2612,7 +2612,7 @@
         <v>7309.102498648497</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>7441.48386788546</v>
+        <v>7441.483867885459</v>
       </c>
       <c r="G13" s="157" t="n">
         <v>7748.349288182523</v>
@@ -2642,7 +2642,7 @@
         <v>85434699.9260983</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>99685267.95342554</v>
+        <v>99685267.95342553</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>119229900.0864305</v>
@@ -2662,7 +2662,7 @@
         <v>4687.085844867526</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4771.977641362306</v>
+        <v>4771.977641362305</v>
       </c>
       <c r="X13" s="157" t="n">
         <v>4968.760292586534</v>
@@ -2677,7 +2677,7 @@
         <v>4684.407927144372</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4769.566888410653</v>
+        <v>4769.566888410652</v>
       </c>
       <c r="AC13" s="157" t="n">
         <v>4966.545832977391</v>
@@ -2692,7 +2692,7 @@
         <v>85434699.9260983</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>99685267.95342554</v>
+        <v>99685267.95342553</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>119229900.0864305</v>
@@ -2746,7 +2746,7 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>960.3310149489649</v>
+        <v>960.3310149489646</v>
       </c>
       <c r="D14" s="168" t="n">
         <v>1015.745368357932</v>
@@ -2761,7 +2761,7 @@
         <v>1229.959464598855</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>952.7621442772797</v>
+        <v>952.7621442772793</v>
       </c>
       <c r="I14" s="168" t="n">
         <v>1009.767465558283</v>
@@ -2823,7 +2823,7 @@
         <v>1294.657713841785</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>1375.045483100415</v>
+        <v>1375.045483100416</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>152674515.2106922</v>
@@ -3724,7 +3724,7 @@
         <v>996.0481292993957</v>
       </c>
       <c r="J23" s="86" t="n">
-        <v>719.164016821238</v>
+        <v>719.1640168212379</v>
       </c>
       <c r="K23" s="86" t="n">
         <v>416.8898058374645</v>
@@ -3733,13 +3733,13 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M23" s="85" t="n">
-        <v>150951.1467452348</v>
+        <v>150951.1467452349</v>
       </c>
       <c r="N23" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.6660005071</v>
       </c>
       <c r="O23" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.2283848732</v>
       </c>
       <c r="P23" s="86" t="n">
         <v>183132.2484568503</v>
@@ -3765,16 +3765,16 @@
         <v>154104.2991247607</v>
       </c>
       <c r="X23" s="87" t="n">
-        <v>169506.0006699098</v>
+        <v>169506.0006699097</v>
       </c>
       <c r="Y23" s="85" t="n">
         <v>1057.63037909861</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>840.486018876822</v>
+        <v>840.4860188768221</v>
       </c>
       <c r="AA23" s="86" t="n">
-        <v>607.685870427589</v>
+        <v>607.6858704275888</v>
       </c>
       <c r="AB23" s="86" t="n">
         <v>353.7984904589192</v>
@@ -3795,7 +3795,7 @@
         <v>154458.0976152196</v>
       </c>
       <c r="AH23" s="87" t="n">
-        <v>169570.7670613156</v>
+        <v>169570.7670613155</v>
       </c>
       <c r="AR23" s="90" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>1004.844413619396</v>
       </c>
       <c r="J25" s="92" t="n">
-        <v>728.145787461238</v>
+        <v>728.1457874612379</v>
       </c>
       <c r="K25" s="92" t="n">
         <v>425.9909164274645</v>
@@ -3978,7 +3978,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O25" s="92" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P25" s="92" t="n">
         <v>196537.2353508696</v>
@@ -4010,10 +4010,10 @@
         <v>1067.689752732331</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>850.6909766208969</v>
+        <v>850.690976620897</v>
       </c>
       <c r="AA25" s="92" t="n">
-        <v>618.1060190396307</v>
+        <v>618.1060190396306</v>
       </c>
       <c r="AB25" s="92" t="n">
         <v>364.3570906151159</v>
@@ -4417,7 +4417,7 @@
         <v>550.0770895093377</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>585.8601993231206</v>
+        <v>585.8601993231207</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>619.101549534911</v>
@@ -4432,7 +4432,7 @@
         <v>547.7238670867836</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>584.5310081222486</v>
+        <v>584.5310081222487</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>618.9532326178842</v>
@@ -4447,7 +4447,7 @@
         <v>72490158.76493734</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>83234908.58156249</v>
+        <v>83234908.5815625</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>96726006.1215378</v>
@@ -4467,7 +4467,7 @@
         <v>675.003539160416</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>718.9132496848337</v>
+        <v>718.9132496848338</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>759.7039487838342</v>
@@ -4482,7 +4482,7 @@
         <v>672.1484114461177</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>717.3005995844295</v>
+        <v>717.3005995844296</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>759.5240064246059</v>
@@ -4497,7 +4497,7 @@
         <v>72490158.76493734</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>83234908.58156249</v>
+        <v>83234908.5815625</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>96726006.1215378</v>
@@ -4513,7 +4513,7 @@
         <v>1050.076658642545</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1129.291770222149</v>
+        <v>1129.291770222148</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1204.387878513268</v>
@@ -4543,7 +4543,7 @@
         <v>27024826.45465692</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>29907196.83777045</v>
+        <v>29907196.83777044</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>33272062.72166796</v>
@@ -4593,7 +4593,7 @@
         <v>27024826.45465692</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>29907196.83777045</v>
+        <v>29907196.83777044</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>33272062.72166796</v>
@@ -4723,7 +4723,7 @@
         <v>1367.876864801452</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>1424.367626292859</v>
+        <v>1424.367626292858</v>
       </c>
       <c r="G38" s="157" t="n">
         <v>1463.669928991915</v>
@@ -4738,7 +4738,7 @@
         <v>1366.741877365136</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>1424.367626292859</v>
+        <v>1424.367626292858</v>
       </c>
       <c r="L38" s="157" t="n">
         <v>1463.669928991915</v>
@@ -4773,7 +4773,7 @@
         <v>1664.524659706382</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1733.266421459687</v>
+        <v>1733.266421459686</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1781.092109362757</v>
@@ -4788,7 +4788,7 @@
         <v>1663.040917171216</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>1733.266421459687</v>
+        <v>1733.266421459686</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>1781.092109362757</v>
@@ -4816,34 +4816,34 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>614.3754204850399</v>
+        <v>614.3754204850397</v>
       </c>
       <c r="D39" s="162" t="n">
         <v>661.1031635090523</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>705.2137826973254</v>
+        <v>705.2137826973253</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>747.5977618608003</v>
+        <v>747.5977618608005</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>786.0914493778482</v>
+        <v>786.0914493778481</v>
       </c>
       <c r="H39" s="161" t="n">
-        <v>609.270397430194</v>
+        <v>609.2703974301938</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>656.9942914712622</v>
+        <v>656.994291471262</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>702.2334121458072</v>
+        <v>702.2334121458071</v>
       </c>
       <c r="K39" s="162" t="n">
         <v>745.8958994722102</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>785.8093760127343</v>
+        <v>785.8093760127342</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>91970065.17001276</v>
@@ -4927,7 +4927,7 @@
         <v>7744.334073583914</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7984.424750950066</v>
+        <v>7984.424750950065</v>
       </c>
       <c r="G40" s="157" t="n">
         <v>8334.24684111275</v>
@@ -4942,7 +4942,7 @@
         <v>7738.387836697953</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7979.003848025621</v>
+        <v>7979.00384802562</v>
       </c>
       <c r="L40" s="157" t="n">
         <v>8329.254909106083</v>
@@ -4957,7 +4957,7 @@
         <v>90522038.48919083</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>106958442.0101133</v>
+        <v>106958442.0101132</v>
       </c>
       <c r="Q40" s="160" t="n">
         <v>128245563.1778321</v>
@@ -4977,7 +4977,7 @@
         <v>4966.185468179197</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>5120.147683865135</v>
+        <v>5120.147683865134</v>
       </c>
       <c r="X40" s="157" t="n">
         <v>5344.477027628842</v>
@@ -4992,7 +4992,7 @@
         <v>4963.348089790604</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>5117.561039067225</v>
+        <v>5117.561039067224</v>
       </c>
       <c r="AC40" s="157" t="n">
         <v>5342.095119906842</v>
@@ -5007,7 +5007,7 @@
         <v>90522038.48919083</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>106958442.0101133</v>
+        <v>106958442.0101132</v>
       </c>
       <c r="AH40" s="160" t="n">
         <v>128245563.1778321</v>
@@ -5020,7 +5020,7 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>987.6409243149578</v>
+        <v>987.6409243149576</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>1069.181638815776</v>
@@ -5035,7 +5035,7 @@
         <v>1322.796854742798</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>979.8568099732994</v>
+        <v>979.8568099732993</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>1062.889250869826</v>
@@ -5097,7 +5097,7 @@
         <v>1388.904499568508</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>1478.833971790076</v>
+        <v>1478.833971790077</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>157016275.6120497</v>
@@ -5380,40 +5380,40 @@
         <v>0.1943657082330655</v>
       </c>
       <c r="F46" s="149" t="n">
-        <v>0.2141963817335411</v>
+        <v>0.214196381733541</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323322653354024</v>
+        <v>0.2323322653354022</v>
       </c>
       <c r="H46" s="148" t="n">
-        <v>0.1572947229889339</v>
+        <v>0.1572947229889338</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.173828389278059</v>
+        <v>0.1738283892780591</v>
       </c>
       <c r="J46" s="149" t="n">
-        <v>0.1935342143360961</v>
+        <v>0.1935342143360962</v>
       </c>
       <c r="K46" s="149" t="n">
-        <v>0.2137104160608639</v>
+        <v>0.2137104160608638</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.2322766059603834</v>
+        <v>0.2322766059603832</v>
       </c>
       <c r="M46" s="151" t="n">
-        <v>18303.07821476197</v>
+        <v>18303.07821476196</v>
       </c>
       <c r="N46" s="152" t="n">
         <v>21609.95508562833</v>
       </c>
       <c r="O46" s="152" t="n">
-        <v>25613.8663416107</v>
+        <v>25613.86634161071</v>
       </c>
       <c r="P46" s="152" t="n">
-        <v>30431.51979378565</v>
+        <v>30431.51979378564</v>
       </c>
       <c r="Q46" s="153" t="n">
-        <v>36298.68498301287</v>
+        <v>36298.68498301286</v>
       </c>
       <c r="S46" s="21" t="inlineStr">
         <is>
@@ -5427,43 +5427,43 @@
         <v>0.2146581425014618</v>
       </c>
       <c r="V46" s="149" t="n">
-        <v>0.2385075536699168</v>
+        <v>0.2385075536699169</v>
       </c>
       <c r="W46" s="149" t="n">
-        <v>0.2628419152567548</v>
+        <v>0.2628419152567547</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850965880117631</v>
+        <v>0.285096588011763</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.1930359802335763</v>
       </c>
       <c r="Z46" s="149" t="n">
-        <v>0.2133212625051747</v>
+        <v>0.2133212625051748</v>
       </c>
       <c r="AA46" s="149" t="n">
         <v>0.2374987152164185</v>
       </c>
       <c r="AB46" s="149" t="n">
-        <v>0.262252314159244</v>
+        <v>0.2622523141592439</v>
       </c>
       <c r="AC46" s="150" t="n">
-        <v>0.2850290604535125</v>
+        <v>0.2850290604535123</v>
       </c>
       <c r="AD46" s="151" t="n">
-        <v>18303.07821476197</v>
+        <v>18303.07821476196</v>
       </c>
       <c r="AE46" s="152" t="n">
         <v>21609.95508562833</v>
       </c>
       <c r="AF46" s="152" t="n">
-        <v>25613.8663416107</v>
+        <v>25613.86634161071</v>
       </c>
       <c r="AG46" s="152" t="n">
-        <v>30431.51979378565</v>
+        <v>30431.51979378564</v>
       </c>
       <c r="AH46" s="153" t="n">
-        <v>36298.68498301287</v>
+        <v>36298.68498301286</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" thickBot="1">
@@ -5581,13 +5581,13 @@
         <v>0.1487184323857965</v>
       </c>
       <c r="E48" s="162" t="n">
-        <v>0.1652451100048922</v>
+        <v>0.1652451100048923</v>
       </c>
       <c r="F48" s="162" t="n">
-        <v>0.1817335160110374</v>
+        <v>0.1817335160110373</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.1967463162252991</v>
+        <v>0.196746316225299</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.1333486192288132</v>
@@ -5599,25 +5599,25 @@
         <v>0.1645115251971507</v>
       </c>
       <c r="K48" s="162" t="n">
-        <v>0.1812931161462725</v>
+        <v>0.1812931161462724</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.1966710271097837</v>
+        <v>0.1966710271097836</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>18979.39097050553</v>
       </c>
       <c r="N48" s="165" t="n">
-        <v>22310.41968938967</v>
+        <v>22310.41968938968</v>
       </c>
       <c r="O48" s="165" t="n">
-        <v>26341.313426504</v>
+        <v>26341.31342650401</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>31188.20939906547</v>
+        <v>31188.20939906546</v>
       </c>
       <c r="Q48" s="166" t="n">
-        <v>37085.7900061697</v>
+        <v>37085.79000616969</v>
       </c>
       <c r="S48" s="42" t="inlineStr">
         <is>
@@ -5625,49 +5625,49 @@
         </is>
       </c>
       <c r="T48" s="161" t="n">
-        <v>0.1588714574006971</v>
+        <v>0.158871457400697</v>
       </c>
       <c r="U48" s="162" t="n">
-        <v>0.1758788068887239</v>
+        <v>0.175878806888724</v>
       </c>
       <c r="V48" s="162" t="n">
-        <v>0.195553468015242</v>
+        <v>0.1955534680152421</v>
       </c>
       <c r="W48" s="162" t="n">
-        <v>0.2151173946579932</v>
+        <v>0.2151173946579931</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.232935874254144</v>
+        <v>0.2329358742541439</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.1575202293853196</v>
       </c>
       <c r="Z48" s="162" t="n">
-        <v>0.174749743740845</v>
+        <v>0.1747497437408451</v>
       </c>
       <c r="AA48" s="162" t="n">
         <v>0.1946858115605125</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.2145937241929916</v>
+        <v>0.2145937241929914</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2328411549957266</v>
+        <v>0.2328411549957265</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>18979.39097050553</v>
       </c>
       <c r="AE48" s="165" t="n">
-        <v>22310.41968938967</v>
+        <v>22310.41968938968</v>
       </c>
       <c r="AF48" s="165" t="n">
-        <v>26341.313426504</v>
+        <v>26341.31342650401</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>31188.20939906547</v>
+        <v>31188.20939906546</v>
       </c>
       <c r="AH48" s="166" t="n">
-        <v>37085.7900061697</v>
+        <v>37085.79000616969</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" thickBot="1">
@@ -5788,10 +5788,10 @@
         <v>0.1648148442278476</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.1802779008783004</v>
+        <v>0.1802779008783003</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.1941561571758201</v>
+        <v>0.19415615717582</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.134513039340199</v>
@@ -5803,7 +5803,7 @@
         <v>0.164118304653265</v>
       </c>
       <c r="K50" s="162" t="n">
-        <v>0.179867508827052</v>
+        <v>0.1798675088270519</v>
       </c>
       <c r="L50" s="163" t="n">
         <v>0.1940864880798701</v>
@@ -5812,16 +5812,16 @@
         <v>20304.89754058993</v>
       </c>
       <c r="N50" s="165" t="n">
-        <v>23755.19112936988</v>
+        <v>23755.19112936989</v>
       </c>
       <c r="O50" s="165" t="n">
         <v>27927.72114837499</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>32939.54131583039</v>
+        <v>32939.54131583038</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="T50" s="161" t="n">
-        <v>0.1604893368708297</v>
+        <v>0.1604893368708296</v>
       </c>
       <c r="U50" s="162" t="n">
         <v>0.1766843000438436</v>
@@ -5838,10 +5838,10 @@
         <v>0.1953625521188488</v>
       </c>
       <c r="W50" s="162" t="n">
-        <v>0.2137483607070754</v>
+        <v>0.2137483607070753</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.230257588318819</v>
+        <v>0.2302575883188189</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.1591588515303609</v>
@@ -5850,28 +5850,28 @@
         <v>0.1755866562320332</v>
       </c>
       <c r="AA50" s="162" t="n">
-        <v>0.1945355930157594</v>
+        <v>0.1945355930157595</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.2132587531790543</v>
+        <v>0.2132587531790542</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2301696430122803</v>
+        <v>0.2301696430122802</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20304.89754058993</v>
       </c>
       <c r="AE50" s="165" t="n">
-        <v>23755.19112936988</v>
+        <v>23755.19112936989</v>
       </c>
       <c r="AF50" s="165" t="n">
         <v>27927.72114837499</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>32939.54131583039</v>
+        <v>32939.54131583038</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5989,10 +5989,10 @@
         <v>0.1399546015089556</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.1541793590449601</v>
+        <v>0.1541793590449602</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1679635525786576</v>
+        <v>0.1679635525786575</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.1803508426806718</v>
@@ -6007,7 +6007,7 @@
         <v>0.1535620636778062</v>
       </c>
       <c r="K52" s="180" t="n">
-        <v>0.1675994946048001</v>
+        <v>0.1675994946048</v>
       </c>
       <c r="L52" s="181" t="n">
         <v>0.1802830472300986</v>
@@ -6016,16 +6016,16 @@
         <v>20304.89754058993</v>
       </c>
       <c r="N52" s="183" t="n">
-        <v>23755.19112936988</v>
+        <v>23755.19112936989</v>
       </c>
       <c r="O52" s="183" t="n">
         <v>27927.72114837499</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>32939.54131583039</v>
+        <v>32939.54131583038</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6042,22 +6042,22 @@
         <v>0.1732693368414499</v>
       </c>
       <c r="W52" s="186" t="n">
-        <v>0.1882323854753558</v>
+        <v>0.1882323854753557</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2017036616725109</v>
+        <v>0.2017036616725108</v>
       </c>
       <c r="Y52" s="185" t="n">
-        <v>0.1429274200203805</v>
+        <v>0.1429274200203804</v>
       </c>
       <c r="Z52" s="186" t="n">
-        <v>0.1566673358028069</v>
+        <v>0.156667335802807</v>
       </c>
       <c r="AA52" s="186" t="n">
         <v>0.1726074120799669</v>
       </c>
       <c r="AB52" s="186" t="n">
-        <v>0.1878412789509086</v>
+        <v>0.1878412789509085</v>
       </c>
       <c r="AC52" s="187" t="n">
         <v>0.2016250280917121</v>
@@ -6066,16 +6066,16 @@
         <v>20304.89754058993</v>
       </c>
       <c r="AE52" s="189" t="n">
-        <v>23755.19112936988</v>
+        <v>23755.19112936989</v>
       </c>
       <c r="AF52" s="189" t="n">
         <v>27927.72114837499</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>32939.54131583039</v>
+        <v>32939.54131583038</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39030.04291982154</v>
+        <v>39030.04291982152</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6337,10 +6337,10 @@
         <v>0.008998740716351445</v>
       </c>
       <c r="D57" s="149" t="n">
-        <v>0.008248840010620564</v>
+        <v>0.008248840010620562</v>
       </c>
       <c r="E57" s="149" t="n">
-        <v>0.007617268941579626</v>
+        <v>0.007617268941579628</v>
       </c>
       <c r="F57" s="149" t="n">
         <v>0.0002766252338232</v>
@@ -6352,13 +6352,13 @@
         <v>0.008922512385849816</v>
       </c>
       <c r="I57" s="149" t="n">
-        <v>0.008196882547161872</v>
+        <v>0.00819688254716187</v>
       </c>
       <c r="J57" s="149" t="n">
-        <v>0.007584682367054335</v>
+        <v>0.007584682367054337</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>0.000275997630468062</v>
+        <v>0.0002759976304680621</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6367,13 +6367,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="O57" s="152" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6387,13 +6387,13 @@
         <v>0.01104241923062504</v>
       </c>
       <c r="U57" s="149" t="n">
-        <v>0.01012221069978303</v>
+        <v>0.01012221069978302</v>
       </c>
       <c r="V57" s="149" t="n">
-        <v>0.00934720531423929</v>
+        <v>0.009347205314239292</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003394488071086405</v>
+        <v>0.0003394488071086406</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6402,13 +6402,13 @@
         <v>0.01094992821005139</v>
       </c>
       <c r="Z57" s="149" t="n">
-        <v>0.01005917008625191</v>
+        <v>0.0100591700862519</v>
       </c>
       <c r="AA57" s="149" t="n">
-        <v>0.009307668536436442</v>
+        <v>0.009307668536436444</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003386873631470696</v>
+        <v>0.0003386873631470697</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6417,13 +6417,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="AF57" s="152" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6541,13 +6541,13 @@
         <v>0.00735754791261178</v>
       </c>
       <c r="D59" s="162" t="n">
-        <v>0.006792645179358404</v>
+        <v>0.006792645179358402</v>
       </c>
       <c r="E59" s="162" t="n">
-        <v>0.006297178063092292</v>
+        <v>0.006297178063092293</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002290065443738623</v>
+        <v>0.0002290065443738624</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6556,13 +6556,13 @@
         <v>0.007294632093492824</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006748900463883717</v>
+        <v>0.006748900463883716</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006269222535944825</v>
+        <v>0.006269222535944826</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002284515864696396</v>
+        <v>0.0002284515864696397</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6571,13 +6571,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="O59" s="165" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6591,13 +6591,13 @@
         <v>0.008690819886980068</v>
       </c>
       <c r="U59" s="162" t="n">
-        <v>0.008033182643189949</v>
+        <v>0.008033182643189947</v>
       </c>
       <c r="V59" s="162" t="n">
-        <v>0.00745217216358623</v>
+        <v>0.007452172163586231</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002710743305177864</v>
+        <v>0.0002710743305177865</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
@@ -6606,10 +6606,10 @@
         <v>0.008616903026771072</v>
       </c>
       <c r="Z59" s="162" t="n">
-        <v>0.007981613209424433</v>
+        <v>0.007981613209424431</v>
       </c>
       <c r="AA59" s="162" t="n">
-        <v>0.007419107419988905</v>
+        <v>0.007419107419988907</v>
       </c>
       <c r="AB59" s="162" t="n">
         <v>0.0002704144414328617</v>
@@ -6621,13 +6621,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="AF59" s="165" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6742,31 +6742,31 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.006935607065566464</v>
+        <v>0.006935607065566463</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006398270053439132</v>
+        <v>0.006398270053439131</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.005924007614024657</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.000215093977790845</v>
+        <v>0.0002150939777908451</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="161" t="n">
-        <v>0.006877977100583301</v>
+        <v>0.006877977100583299</v>
       </c>
       <c r="I61" s="162" t="n">
-        <v>0.006358503683583536</v>
+        <v>0.006358503683583533</v>
       </c>
       <c r="J61" s="162" t="n">
         <v>0.005898971606117552</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>0.000214604328985713</v>
+        <v>0.0002146043289857131</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6775,13 +6775,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="O61" s="165" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6795,10 +6795,10 @@
         <v>0.008206208032320359</v>
       </c>
       <c r="U61" s="162" t="n">
-        <v>0.007579163951272275</v>
+        <v>0.007579163951272274</v>
       </c>
       <c r="V61" s="162" t="n">
-        <v>0.007021996420707131</v>
+        <v>0.007021996420707132</v>
       </c>
       <c r="W61" s="162" t="n">
         <v>0.0002550284029643438</v>
@@ -6810,13 +6810,13 @@
         <v>0.008138177098298699</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007532078712755066</v>
+        <v>0.007532078712755064</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.006992272690140629</v>
+        <v>0.006992272690140631</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>0.000254444240234218</v>
+        <v>0.0002544442402342181</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6825,13 +6825,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="AF61" s="165" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6946,31 +6946,31 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006530576897486652</v>
+        <v>0.006530576897486651</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006003583059208623</v>
+        <v>0.006003583059208621</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.005541732003490626</v>
+        <v>0.005541732003490627</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002004014273075765</v>
+        <v>0.0002004014273075766</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="179" t="n">
-        <v>0.006479106007575636</v>
+        <v>0.006479106007575635</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.005968250546656203</v>
+        <v>0.0059682505466562</v>
       </c>
       <c r="J63" s="180" t="n">
         <v>0.005519544302666382</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>0.0001999670608247077</v>
+        <v>0.0001999670608247078</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
@@ -6979,13 +6979,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="O63" s="183" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -6999,13 +6999,13 @@
         <v>0.007363565867330987</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006758420575351567</v>
+        <v>0.006758420575351565</v>
       </c>
       <c r="V63" s="186" t="n">
-        <v>0.006227890913191911</v>
+        <v>0.006227890913191913</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002245846681357013</v>
+        <v>0.0002245846681357014</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
@@ -7014,13 +7014,13 @@
         <v>0.007308224739903297</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006720503313332603</v>
+        <v>0.006720503313332601</v>
       </c>
       <c r="AA63" s="186" t="n">
-        <v>0.006204099079723829</v>
+        <v>0.006204099079723831</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.0002241180293648179</v>
+        <v>0.000224118029364818</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7029,13 +7029,13 @@
         <v>1038.238530620515</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1019.018035097775</v>
+        <v>1019.018035097774</v>
       </c>
       <c r="AF63" s="189" t="n">
-        <v>1003.817547505693</v>
+        <v>1003.817547505694</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>39.30097329572723</v>
+        <v>39.30097329572725</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7306,7 +7306,7 @@
         <v>0.007296019909008172</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.008900514969487126</v>
+        <v>0.008900514969487124</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.01031571117551498</v>
@@ -7321,7 +7321,7 @@
         <v>0.00726480763354221</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.008880321609032977</v>
+        <v>0.008880321609032975</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.01031323986126994</v>
@@ -7510,7 +7510,7 @@
         <v>0.006031602254201518</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007368366754324399</v>
+        <v>0.007368366754324398</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.00855026575881042</v>
@@ -7525,7 +7525,7 @@
         <v>0.006004825717335216</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007350510787008247</v>
+        <v>0.007350510787008246</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.008546993819804125</v>
@@ -7560,7 +7560,7 @@
         <v>0.007137885886382586</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008721912687688115</v>
+        <v>0.008721912687688113</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01012300340786597</v>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.003440055496924462</v>
+        <v>0.003440055496924461</v>
       </c>
       <c r="D72" s="162" t="n">
         <v>0.005021963276029011</v>
@@ -7720,16 +7720,16 @@
         <v>0.009456307483938458</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.003411471080887954</v>
+        <v>0.003411471080887953</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.004990750894030779</v>
+        <v>0.004990750894030778</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0066303267744339</v>
+        <v>0.006630326774433898</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.008125972548769093</v>
+        <v>0.008125972548769091</v>
       </c>
       <c r="L72" s="163" t="n">
         <v>0.009452914275074963</v>
@@ -7779,10 +7779,10 @@
         <v>0.007859175450768986</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009634507006954701</v>
+        <v>0.009634507006954699</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.01121033167040624</v>
+        <v>0.01121033167040625</v>
       </c>
       <c r="AD72" s="164" t="n">
         <v>514.9654717482424</v>
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003239160861033004</v>
+        <v>0.003239160861033003</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.004712175853179222</v>
@@ -7918,22 +7918,22 @@
         <v>0.006228796565383722</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007588181024735638</v>
+        <v>0.007588181024735637</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.008783924487295315</v>
       </c>
       <c r="H74" s="179" t="n">
-        <v>0.003213631341252529</v>
+        <v>0.003213631341252528</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004684443578829109</v>
+        <v>0.004684443578829108</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.006203858030896533</v>
+        <v>0.006203858030896531</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007571733779087892</v>
+        <v>0.007571733779087891</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.008780622533672225</v>
@@ -7968,10 +7968,10 @@
         <v>0.007000025534479076</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008503877143441129</v>
+        <v>0.008503877143441127</v>
       </c>
       <c r="X74" s="187" t="n">
-        <v>0.00982390604117857</v>
+        <v>0.009823906041178571</v>
       </c>
       <c r="Y74" s="185" t="n">
         <v>0.003624873562125642</v>
@@ -7983,10 +7983,10 @@
         <v>0.006973283986801054</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008486207910670701</v>
+        <v>0.008486207910670699</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.009820076220227165</v>
+        <v>0.009820076220227167</v>
       </c>
       <c r="AD74" s="188" t="n">
         <v>514.9654717482424</v>
@@ -8269,7 +8269,7 @@
         <v>550.2863685064214</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>586.0835728450575</v>
+        <v>586.0835728450576</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>619.344197511422</v>
@@ -8284,7 +8284,7 @@
         <v>547.9322507911202</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>584.7538748575489</v>
+        <v>584.753874857549</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>619.1958224637058</v>
@@ -8299,7 +8299,7 @@
         <v>72517737.93159248</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>83266643.92507863</v>
+        <v>83266643.92507865</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>96763916.49291226</v>
@@ -8319,7 +8319,7 @@
         <v>675.260346917724</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>719.1873529346101</v>
+        <v>719.1873529346102</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>760.0017038549663</v>
@@ -8334,7 +8334,7 @@
         <v>672.4041329588318</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>717.5740879719351</v>
+        <v>717.5740879719352</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>759.8216909699099</v>
@@ -8349,7 +8349,7 @@
         <v>72517737.93159248</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>83266643.92507863</v>
+        <v>83266643.92507865</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>96763916.49291226</v>
@@ -8415,7 +8415,7 @@
         <v>1062.278252283267</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>1142.411988273388</v>
+        <v>1142.411988273387</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1218.378672424265</v>
@@ -8473,7 +8473,7 @@
         <v>663.6482839852575</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>704.012711444808</v>
+        <v>704.0127114448082</v>
       </c>
       <c r="G81" s="163" t="n">
         <v>741.2609450231503</v>
@@ -8488,7 +8488,7 @@
         <v>660.7021011977553</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>702.3066579346003</v>
+        <v>702.3066579346004</v>
       </c>
       <c r="L81" s="163" t="n">
         <v>740.9772859336809</v>
@@ -8503,7 +8503,7 @@
         <v>105790528.1003453</v>
       </c>
       <c r="P81" s="165" t="n">
-        <v>120819188.1502529</v>
+        <v>120819188.150253</v>
       </c>
       <c r="Q81" s="166" t="n">
         <v>139724332.7057961</v>
@@ -8523,7 +8523,7 @@
         <v>785.3710374354746</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>833.3376452306068</v>
+        <v>833.337645230607</v>
       </c>
       <c r="X81" s="163" t="n">
         <v>877.6086362994266</v>
@@ -8538,7 +8538,7 @@
         <v>781.886403504383</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>831.3090119214543</v>
+        <v>831.3090119214545</v>
       </c>
       <c r="AC81" s="163" t="n">
         <v>877.2517722505669</v>
@@ -8553,7 +8553,7 @@
         <v>105790528.1003453</v>
       </c>
       <c r="AG81" s="165" t="n">
-        <v>120819188.1502529</v>
+        <v>120819188.150253</v>
       </c>
       <c r="AH81" s="166" t="n">
         <v>139724332.7057961</v>
@@ -8575,7 +8575,7 @@
         <v>1368.051459078482</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1424.545543840335</v>
+        <v>1424.545543840334</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1463.848203355944</v>
@@ -8590,7 +8590,7 @@
         <v>1366.916326773636</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>1424.545543840335</v>
+        <v>1424.545543840334</v>
       </c>
       <c r="L82" s="157" t="n">
         <v>1463.848203355944</v>
@@ -8668,34 +8668,34 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>614.5214362598645</v>
+        <v>614.5214362598643</v>
       </c>
       <c r="D83" s="162" t="n">
         <v>661.2637392261728</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>705.3911800159166</v>
+        <v>705.3911800159165</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>747.7863993687106</v>
+        <v>747.7863993687108</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>786.2950618425077</v>
+        <v>786.2950618425079</v>
       </c>
       <c r="H83" s="161" t="n">
-        <v>609.4151999177157</v>
+        <v>609.4151999177155</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>657.1538691821554</v>
+        <v>657.1538691821553</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>702.4100597488408</v>
+        <v>702.4100597488406</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>746.0841075579149</v>
+        <v>746.084107557915</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>786.0129154150891</v>
+        <v>786.0129154150892</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>91991923.27155572</v>
@@ -8710,7 +8710,7 @@
         <v>136632060.1550035</v>
       </c>
       <c r="Q83" s="166" t="n">
-        <v>158064160.6105025</v>
+        <v>158064160.6105026</v>
       </c>
       <c r="S83" s="42" t="inlineStr">
         <is>
@@ -8724,13 +8724,13 @@
         <v>783.3095903685113</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>836.1323387808748</v>
+        <v>836.1323387808746</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>886.6206908633228</v>
+        <v>886.620690863323</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>932.4989085095066</v>
+        <v>932.4989085095069</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>721.0737620665928</v>
@@ -8739,13 +8739,13 @@
         <v>778.4433123552051</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>832.5930358722928</v>
+        <v>832.5930358722927</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>884.5898160378505</v>
+        <v>884.5898160378507</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>932.1427469473419</v>
+        <v>932.1427469473423</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>91991923.27155572</v>
@@ -8760,7 +8760,7 @@
         <v>136632060.1550035</v>
       </c>
       <c r="AH83" s="166" t="n">
-        <v>158064160.6105025</v>
+        <v>158064160.6105026</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" thickBot="1">
@@ -8779,7 +8779,7 @@
         <v>7744.334073583914</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7984.424750950066</v>
+        <v>7984.424750950065</v>
       </c>
       <c r="G84" s="157" t="n">
         <v>8334.24684111275</v>
@@ -8794,7 +8794,7 @@
         <v>7738.387836697953</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7979.003848025621</v>
+        <v>7979.00384802562</v>
       </c>
       <c r="L84" s="157" t="n">
         <v>8329.254909106083</v>
@@ -8809,7 +8809,7 @@
         <v>90522038.48919083</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>106958442.0101133</v>
+        <v>106958442.0101132</v>
       </c>
       <c r="Q84" s="160" t="n">
         <v>128245563.1778321</v>
@@ -8829,7 +8829,7 @@
         <v>4966.185468179197</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>5120.147683865135</v>
+        <v>5120.147683865134</v>
       </c>
       <c r="X84" s="157" t="n">
         <v>5344.477027628842</v>
@@ -8844,7 +8844,7 @@
         <v>4963.348089790604</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>5117.561039067225</v>
+        <v>5117.561039067224</v>
       </c>
       <c r="AC84" s="157" t="n">
         <v>5342.095119906842</v>
@@ -8859,7 +8859,7 @@
         <v>90522038.48919083</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>106958442.0101133</v>
+        <v>106958442.0101132</v>
       </c>
       <c r="AH84" s="160" t="n">
         <v>128245563.1778321</v>
@@ -8872,13 +8872,13 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>987.7784129640009</v>
+        <v>987.7784129640007</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>1069.332309176198</v>
       </c>
       <c r="E85" s="180" t="n">
-        <v>1159.613451064754</v>
+        <v>1159.613451064753</v>
       </c>
       <c r="F85" s="180" t="n">
         <v>1242.103699191743</v>
@@ -8887,13 +8887,13 @@
         <v>1322.985989509966</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>979.9932150024373</v>
+        <v>979.9932150024371</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>1063.039034499382</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>1154.970650527343</v>
+        <v>1154.970650527342</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>1239.411461803891</v>
@@ -8908,7 +8908,7 @@
         <v>181503095.3710054</v>
       </c>
       <c r="O85" s="183" t="n">
-        <v>210049913.956364</v>
+        <v>210049913.9563639</v>
       </c>
       <c r="P85" s="183" t="n">
         <v>243590502.1651167</v>
@@ -8958,7 +8958,7 @@
         <v>181503095.3710054</v>
       </c>
       <c r="AF85" s="189" t="n">
-        <v>210049913.956364</v>
+        <v>210049913.9563639</v>
       </c>
       <c r="AG85" s="189" t="n">
         <v>243590502.1651167</v>
@@ -9777,7 +9777,7 @@
         <v>996.0481292993957</v>
       </c>
       <c r="J94" s="86" t="n">
-        <v>719.164016821238</v>
+        <v>719.1640168212379</v>
       </c>
       <c r="K94" s="86" t="n">
         <v>416.8898058374645</v>
@@ -9786,13 +9786,13 @@
         <v>72.15937027183648</v>
       </c>
       <c r="M94" s="85" t="n">
-        <v>150951.1467452348</v>
+        <v>150951.1467452349</v>
       </c>
       <c r="N94" s="86" t="n">
-        <v>160260.666000507</v>
+        <v>160260.6660005071</v>
       </c>
       <c r="O94" s="86" t="n">
-        <v>170168.2283848731</v>
+        <v>170168.2283848732</v>
       </c>
       <c r="P94" s="86" t="n">
         <v>183132.2484568503</v>
@@ -9818,16 +9818,16 @@
         <v>154104.2991247607</v>
       </c>
       <c r="X94" s="87" t="n">
-        <v>169506.0006699098</v>
+        <v>169506.0006699097</v>
       </c>
       <c r="Y94" s="85" t="n">
         <v>1057.63037909861</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>840.486018876822</v>
+        <v>840.4860188768221</v>
       </c>
       <c r="AA94" s="86" t="n">
-        <v>607.685870427589</v>
+        <v>607.6858704275888</v>
       </c>
       <c r="AB94" s="86" t="n">
         <v>353.7984904589192</v>
@@ -9848,7 +9848,7 @@
         <v>154458.0976152196</v>
       </c>
       <c r="AH94" s="87" t="n">
-        <v>169570.7670613156</v>
+        <v>169570.7670613155</v>
       </c>
       <c r="AJ94" s="126" t="n">
         <v>37.51602533606992</v>
@@ -10009,7 +10009,7 @@
         <v>1004.844413619396</v>
       </c>
       <c r="J96" s="133" t="n">
-        <v>728.145787461238</v>
+        <v>728.1457874612379</v>
       </c>
       <c r="K96" s="133" t="n">
         <v>425.9909164274645</v>
@@ -10024,7 +10024,7 @@
         <v>170739.8218509265</v>
       </c>
       <c r="O96" s="133" t="n">
-        <v>181866.0187256345</v>
+        <v>181866.0187256346</v>
       </c>
       <c r="P96" s="133" t="n">
         <v>196537.2353508696</v>
@@ -10056,10 +10056,10 @@
         <v>1067.689752732331</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>850.6909766208969</v>
+        <v>850.690976620897</v>
       </c>
       <c r="AA96" s="136" t="n">
-        <v>618.1060190396307</v>
+        <v>618.1060190396306</v>
       </c>
       <c r="AB96" s="136" t="n">
         <v>364.3570906151159</v>
